--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633551.7874482041</v>
+        <v>633552</v>
       </c>
       <c r="R2" t="n">
-        <v>7234518.546784557</v>
+        <v>7234519</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2005-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79017</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633551.7874482041</v>
+        <v>633552</v>
       </c>
       <c r="R3" t="n">
-        <v>7234518.546784557</v>
+        <v>7234519</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -860,19 +840,9 @@
           <t>2005-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83106</v>
+        <v>83107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83112</v>
+        <v>83115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79031</v>
+        <v>79033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83122</v>
+        <v>83156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79033</v>
+        <v>79067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52622-2024 artfynd.xlsx
+++ b/artfynd/A 52622-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>391060</v>
       </c>
       <c r="B2" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>1973547</v>
       </c>
       <c r="B3" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
